--- a/Excel - basic.xlsx
+++ b/Excel - basic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\Hitesh Git hub\Data-Analytics\Data-Analytics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA217A00-3612-482B-B62D-FC2F8B0E51CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3734C245-0387-4547-9984-4F3C4AB13CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{9877E020-D8B8-4241-860F-9552F5AF7DF9}"/>
   </bookViews>
@@ -12746,9 +12746,10 @@
     <col min="10" max="10" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.85546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
